--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574110159</v>
+        <v>46157.93116276844</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116276844</v>
+        <v>46157.93182785375</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93182785375</v>
+        <v>46157.93405386719</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405386719</v>
+        <v>46157.93723476177</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723476177</v>
+        <v>46158.2822126989</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822126989</v>
+        <v>46158.29701399155</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701399155</v>
+        <v>46158.29820976081</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820976081</v>
+        <v>46158.33392326995</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392326995</v>
+        <v>46158.36862064015</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862064015</v>
+        <v>46158.37292892677</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
